--- a/Hoadon/HDVao/7/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/7/HDDienTuKhongMa.xlsx
@@ -325,52 +325,50 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K25TEA</t>
+          <t>K25TBB</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>210510</t>
+          <t>4448911</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>05/07/2025</t>
+          <t>17/07/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0100112437-005</t>
+          <t>0100233488</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
         </is>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>50000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>5000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="M7" s="13"/>
-      <c r="N7" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>55000.0</v>
+        <v>16500.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -404,52 +402,50 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>K25TEA</t>
+          <t>K25TBB</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>261527</t>
+          <t>4499810</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0100112437-005</t>
+          <t>0100233488</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
         </is>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>40000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>4000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="M8" s="13"/>
-      <c r="N8" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>44000.0</v>
+        <v>16500.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -483,52 +479,54 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>K25TEA</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>317320</t>
+          <t>537872</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0100112437-005</t>
+          <t>0303217354-013</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
-        </is>
-      </c>
-      <c r="H9" s="6"/>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN THẾ GIỚI DI ĐỘNG</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Số 290 Trương Công Định, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>20000.0</v>
+        <v>1.7583333E7</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>2000.0</v>
+        <v>1406667.0</v>
       </c>
       <c r="M9" s="13"/>
-      <c r="N9" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>22000.0</v>
+        <v>1.899E7</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -546,401 +544,6 @@
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>K25TEA</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>318433</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>22/07/2025</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>0100112437-005</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
-        </is>
-      </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>20000.0</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>2000.0</v>
-      </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O10" s="13" t="n">
-        <v>22000.0</v>
-      </c>
-      <c r="P10" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S10" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>K25TEA</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>325189</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>24/07/2025</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>0100112437-005</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
-        </is>
-      </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>20000.0</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>2000.0</v>
-      </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O11" s="13" t="n">
-        <v>22000.0</v>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S11" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>K25TEA</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>326449</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>25/07/2025</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>0100112437-005</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
-        </is>
-      </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K12" s="13" t="n">
-        <v>20000.0</v>
-      </c>
-      <c r="L12" s="13" t="n">
-        <v>2000.0</v>
-      </c>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O12" s="13" t="n">
-        <v>22000.0</v>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S12" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>K25THA</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>857839</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>02/07/2025</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>0106869738-044</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
-        </is>
-      </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Công Ty Cổ Phần Đầu Tư Xây Dựng Thương Mại Dịch Vụ Kỹ Thuật H Và V</t>
-        </is>
-      </c>
-      <c r="K13" s="13" t="n">
-        <v>398182.0</v>
-      </c>
-      <c r="L13" s="13" t="n">
-        <v>39818.0</v>
-      </c>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13" t="n">
-        <v>438000.0</v>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>K25TVT</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>4814773</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>29/07/2025</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>0310471746-364</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>CN CÔNG TY CP THƯƠNG MẠI BÁCH HÓA XANH - CH BÁCH HÓA XANH BÀ RỊA VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Số 290 Trương Công Định, Phường Tam Thắng, Thành Phố Hồ Chí Minh. Việt Nam</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K14" s="13" t="n">
-        <v>193500.0</v>
-      </c>
-      <c r="L14" s="13" t="n">
-        <v>9675.0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13" t="n">
-        <v>203175.0</v>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>
